--- a/review-results/河北实时运行及市场出清数据-20260813.xlsx
+++ b/review-results/河北实时运行及市场出清数据-20260813.xlsx
@@ -4238,8 +4238,12 @@
       <s:c r="C2" s="1" t="n">
         <s:v>1</s:v>
       </s:c>
-      <s:c r="D2" s="1"/>
-      <s:c r="E2" s="1"/>
+      <s:c r="D2" s="1" t="n">
+        <s:v>398.01</s:v>
+      </s:c>
+      <s:c r="E2" s="1" t="n">
+        <s:v>396.26</s:v>
+      </s:c>
       <s:c r="F2" s="1" t="n">
         <s:v>70</s:v>
       </s:c>
@@ -4284,8 +4288,12 @@
       <s:c r="C3" s="1" t="n">
         <s:v>1</s:v>
       </s:c>
-      <s:c r="D3" s="1"/>
-      <s:c r="E3" s="1"/>
+      <s:c r="D3" s="1" t="n">
+        <s:v>398.01</s:v>
+      </s:c>
+      <s:c r="E3" s="1" t="n">
+        <s:v>389.76</s:v>
+      </s:c>
       <s:c r="F3" s="1" t="n">
         <s:v>100</s:v>
       </s:c>
@@ -4330,8 +4338,12 @@
       <s:c r="C4" s="1" t="n">
         <s:v>1</s:v>
       </s:c>
-      <s:c r="D4" s="1"/>
-      <s:c r="E4" s="1"/>
+      <s:c r="D4" s="1" t="n">
+        <s:v>398.01</s:v>
+      </s:c>
+      <s:c r="E4" s="1" t="n">
+        <s:v>381.83</s:v>
+      </s:c>
       <s:c r="F4" s="1" t="n">
         <s:v>140</s:v>
       </s:c>
@@ -4376,8 +4388,12 @@
       <s:c r="C5" s="1" t="n">
         <s:v>1</s:v>
       </s:c>
-      <s:c r="D5" s="1"/>
-      <s:c r="E5" s="1"/>
+      <s:c r="D5" s="1" t="n">
+        <s:v>398.01</s:v>
+      </s:c>
+      <s:c r="E5" s="1" t="n">
+        <s:v>382.42</s:v>
+      </s:c>
       <s:c r="F5" s="1" t="n">
         <s:v>100</s:v>
       </s:c>
@@ -4422,8 +4438,12 @@
       <s:c r="C6" s="1" t="n">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="D6" s="1"/>
-      <s:c r="E6" s="1"/>
+      <s:c r="D6" s="1" t="n">
+        <s:v>398.01</s:v>
+      </s:c>
+      <s:c r="E6" s="1" t="n">
+        <s:v>401.55</s:v>
+      </s:c>
       <s:c r="F6" s="1" t="n">
         <s:v>70</s:v>
       </s:c>
@@ -4468,8 +4488,12 @@
       <s:c r="C7" s="1" t="n">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="D7" s="1"/>
-      <s:c r="E7" s="1"/>
+      <s:c r="D7" s="1" t="n">
+        <s:v>398.01</s:v>
+      </s:c>
+      <s:c r="E7" s="1" t="n">
+        <s:v>399.66</s:v>
+      </s:c>
       <s:c r="F7" s="1" t="n">
         <s:v>40</s:v>
       </s:c>
@@ -4514,8 +4538,12 @@
       <s:c r="C8" s="1" t="n">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="D8" s="1"/>
-      <s:c r="E8" s="1"/>
+      <s:c r="D8" s="1" t="n">
+        <s:v>398.01</s:v>
+      </s:c>
+      <s:c r="E8" s="1" t="n">
+        <s:v>399.66</s:v>
+      </s:c>
       <s:c r="F8" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -4560,8 +4588,12 @@
       <s:c r="C9" s="1" t="n">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="D9" s="1"/>
-      <s:c r="E9" s="1"/>
+      <s:c r="D9" s="1" t="n">
+        <s:v>398.01</s:v>
+      </s:c>
+      <s:c r="E9" s="1" t="n">
+        <s:v>401.55</s:v>
+      </s:c>
       <s:c r="F9" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -4606,8 +4638,12 @@
       <s:c r="C10" s="1" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="D10" s="1"/>
-      <s:c r="E10" s="1"/>
+      <s:c r="D10" s="1" t="n">
+        <s:v>400.39</s:v>
+      </s:c>
+      <s:c r="E10" s="1" t="n">
+        <s:v>384.54</s:v>
+      </s:c>
       <s:c r="F10" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -4652,8 +4688,12 @@
       <s:c r="C11" s="1" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="D11" s="1"/>
-      <s:c r="E11" s="1"/>
+      <s:c r="D11" s="1" t="n">
+        <s:v>400.39</s:v>
+      </s:c>
+      <s:c r="E11" s="1" t="n">
+        <s:v>381.89</s:v>
+      </s:c>
       <s:c r="F11" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -4698,8 +4738,12 @@
       <s:c r="C12" s="1" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="D12" s="1"/>
-      <s:c r="E12" s="1"/>
+      <s:c r="D12" s="1" t="n">
+        <s:v>400.39</s:v>
+      </s:c>
+      <s:c r="E12" s="1" t="n">
+        <s:v>373.83</s:v>
+      </s:c>
       <s:c r="F12" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -4744,8 +4788,12 @@
       <s:c r="C13" s="1" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="D13" s="1"/>
-      <s:c r="E13" s="1"/>
+      <s:c r="D13" s="1" t="n">
+        <s:v>400.39</s:v>
+      </s:c>
+      <s:c r="E13" s="1" t="n">
+        <s:v>366.07</s:v>
+      </s:c>
       <s:c r="F13" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -4790,8 +4838,12 @@
       <s:c r="C14" s="1" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D14" s="1"/>
-      <s:c r="E14" s="1"/>
+      <s:c r="D14" s="1" t="n">
+        <s:v>400.39</s:v>
+      </s:c>
+      <s:c r="E14" s="1" t="n">
+        <s:v>364.29</s:v>
+      </s:c>
       <s:c r="F14" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -4836,8 +4888,12 @@
       <s:c r="C15" s="1" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D15" s="1"/>
-      <s:c r="E15" s="1"/>
+      <s:c r="D15" s="1" t="n">
+        <s:v>400.39</s:v>
+      </s:c>
+      <s:c r="E15" s="1" t="n">
+        <s:v>364.6</s:v>
+      </s:c>
       <s:c r="F15" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -4882,8 +4938,12 @@
       <s:c r="C16" s="1" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D16" s="1"/>
-      <s:c r="E16" s="1"/>
+      <s:c r="D16" s="1" t="n">
+        <s:v>400.39</s:v>
+      </s:c>
+      <s:c r="E16" s="1" t="n">
+        <s:v>363.36</s:v>
+      </s:c>
       <s:c r="F16" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -4928,8 +4988,12 @@
       <s:c r="C17" s="1" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D17" s="1"/>
-      <s:c r="E17" s="1"/>
+      <s:c r="D17" s="1" t="n">
+        <s:v>400.39</s:v>
+      </s:c>
+      <s:c r="E17" s="1" t="n">
+        <s:v>355.76</s:v>
+      </s:c>
       <s:c r="F17" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -4974,8 +5038,12 @@
       <s:c r="C18" s="1" t="n">
         <s:v>5</s:v>
       </s:c>
-      <s:c r="D18" s="1"/>
-      <s:c r="E18" s="1"/>
+      <s:c r="D18" s="1" t="n">
+        <s:v>400.39</s:v>
+      </s:c>
+      <s:c r="E18" s="1" t="n">
+        <s:v>364.45</s:v>
+      </s:c>
       <s:c r="F18" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -5020,8 +5088,12 @@
       <s:c r="C19" s="1" t="n">
         <s:v>5</s:v>
       </s:c>
-      <s:c r="D19" s="1"/>
-      <s:c r="E19" s="1"/>
+      <s:c r="D19" s="1" t="n">
+        <s:v>400.39</s:v>
+      </s:c>
+      <s:c r="E19" s="1" t="n">
+        <s:v>366.47</s:v>
+      </s:c>
       <s:c r="F19" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -5066,8 +5138,12 @@
       <s:c r="C20" s="1" t="n">
         <s:v>5</s:v>
       </s:c>
-      <s:c r="D20" s="1"/>
-      <s:c r="E20" s="1"/>
+      <s:c r="D20" s="1" t="n">
+        <s:v>400.39</s:v>
+      </s:c>
+      <s:c r="E20" s="1" t="n">
+        <s:v>366.07</s:v>
+      </s:c>
       <s:c r="F20" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -5112,8 +5188,12 @@
       <s:c r="C21" s="1" t="n">
         <s:v>5</s:v>
       </s:c>
-      <s:c r="D21" s="1"/>
-      <s:c r="E21" s="1"/>
+      <s:c r="D21" s="1" t="n">
+        <s:v>400.39</s:v>
+      </s:c>
+      <s:c r="E21" s="1" t="n">
+        <s:v>366.47</s:v>
+      </s:c>
       <s:c r="F21" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -5158,8 +5238,12 @@
       <s:c r="C22" s="1" t="n">
         <s:v>6</s:v>
       </s:c>
-      <s:c r="D22" s="1"/>
-      <s:c r="E22" s="1"/>
+      <s:c r="D22" s="1" t="n">
+        <s:v>413.64</s:v>
+      </s:c>
+      <s:c r="E22" s="1" t="n">
+        <s:v>384.23</s:v>
+      </s:c>
       <s:c r="F22" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -5204,8 +5288,12 @@
       <s:c r="C23" s="1" t="n">
         <s:v>6</s:v>
       </s:c>
-      <s:c r="D23" s="1"/>
-      <s:c r="E23" s="1"/>
+      <s:c r="D23" s="1" t="n">
+        <s:v>413.64</s:v>
+      </s:c>
+      <s:c r="E23" s="1" t="n">
+        <s:v>382.14</s:v>
+      </s:c>
       <s:c r="F23" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -5250,8 +5338,12 @@
       <s:c r="C24" s="1" t="n">
         <s:v>6</s:v>
       </s:c>
-      <s:c r="D24" s="1"/>
-      <s:c r="E24" s="1"/>
+      <s:c r="D24" s="1" t="n">
+        <s:v>413.64</s:v>
+      </s:c>
+      <s:c r="E24" s="1" t="n">
+        <s:v>392.29</s:v>
+      </s:c>
       <s:c r="F24" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -5296,8 +5388,12 @@
       <s:c r="C25" s="1" t="n">
         <s:v>6</s:v>
       </s:c>
-      <s:c r="D25" s="1"/>
-      <s:c r="E25" s="1"/>
+      <s:c r="D25" s="1" t="n">
+        <s:v>413.64</s:v>
+      </s:c>
+      <s:c r="E25" s="1" t="n">
+        <s:v>382.69</s:v>
+      </s:c>
       <s:c r="F25" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -5342,8 +5438,12 @@
       <s:c r="C26" s="1" t="n">
         <s:v>7</s:v>
       </s:c>
-      <s:c r="D26" s="1"/>
-      <s:c r="E26" s="1"/>
+      <s:c r="D26" s="1" t="n">
+        <s:v>413.64</s:v>
+      </s:c>
+      <s:c r="E26" s="1" t="n">
+        <s:v>402.3</s:v>
+      </s:c>
       <s:c r="F26" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -5388,8 +5488,12 @@
       <s:c r="C27" s="1" t="n">
         <s:v>7</s:v>
       </s:c>
-      <s:c r="D27" s="1"/>
-      <s:c r="E27" s="1"/>
+      <s:c r="D27" s="1" t="n">
+        <s:v>413.64</s:v>
+      </s:c>
+      <s:c r="E27" s="1" t="n">
+        <s:v>401.39</s:v>
+      </s:c>
       <s:c r="F27" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -5434,8 +5538,12 @@
       <s:c r="C28" s="1" t="n">
         <s:v>7</s:v>
       </s:c>
-      <s:c r="D28" s="1"/>
-      <s:c r="E28" s="1"/>
+      <s:c r="D28" s="1" t="n">
+        <s:v>413.64</s:v>
+      </s:c>
+      <s:c r="E28" s="1" t="n">
+        <s:v>399.91</s:v>
+      </s:c>
       <s:c r="F28" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -5480,8 +5588,12 @@
       <s:c r="C29" s="1" t="n">
         <s:v>7</s:v>
       </s:c>
-      <s:c r="D29" s="1"/>
-      <s:c r="E29" s="1"/>
+      <s:c r="D29" s="1" t="n">
+        <s:v>413.64</s:v>
+      </s:c>
+      <s:c r="E29" s="1" t="n">
+        <s:v>382.54</s:v>
+      </s:c>
       <s:c r="F29" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -5526,8 +5638,12 @@
       <s:c r="C30" s="1" t="n">
         <s:v>8</s:v>
       </s:c>
-      <s:c r="D30" s="1"/>
-      <s:c r="E30" s="1"/>
+      <s:c r="D30" s="1" t="n">
+        <s:v>474.52</s:v>
+      </s:c>
+      <s:c r="E30" s="1" t="n">
+        <s:v>382.27</s:v>
+      </s:c>
       <s:c r="F30" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -5572,8 +5688,12 @@
       <s:c r="C31" s="1" t="n">
         <s:v>8</s:v>
       </s:c>
-      <s:c r="D31" s="1"/>
-      <s:c r="E31" s="1"/>
+      <s:c r="D31" s="1" t="n">
+        <s:v>474.52</s:v>
+      </s:c>
+      <s:c r="E31" s="1" t="n">
+        <s:v>383.5</s:v>
+      </s:c>
       <s:c r="F31" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -5618,8 +5738,12 @@
       <s:c r="C32" s="1" t="n">
         <s:v>8</s:v>
       </s:c>
-      <s:c r="D32" s="1"/>
-      <s:c r="E32" s="1"/>
+      <s:c r="D32" s="1" t="n">
+        <s:v>474.52</s:v>
+      </s:c>
+      <s:c r="E32" s="1" t="n">
+        <s:v>399.66</s:v>
+      </s:c>
       <s:c r="F32" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -5664,8 +5788,12 @@
       <s:c r="C33" s="1" t="n">
         <s:v>8</s:v>
       </s:c>
-      <s:c r="D33" s="1"/>
-      <s:c r="E33" s="1"/>
+      <s:c r="D33" s="1" t="n">
+        <s:v>474.52</s:v>
+      </s:c>
+      <s:c r="E33" s="1" t="n">
+        <s:v>389.92</s:v>
+      </s:c>
       <s:c r="F33" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -5710,8 +5838,12 @@
       <s:c r="C34" s="1" t="n">
         <s:v>9</s:v>
       </s:c>
-      <s:c r="D34" s="1"/>
-      <s:c r="E34" s="1"/>
+      <s:c r="D34" s="1" t="n">
+        <s:v>437.23</s:v>
+      </s:c>
+      <s:c r="E34" s="1" t="n">
+        <s:v>380.89</s:v>
+      </s:c>
       <s:c r="F34" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -5756,8 +5888,12 @@
       <s:c r="C35" s="1" t="n">
         <s:v>9</s:v>
       </s:c>
-      <s:c r="D35" s="1"/>
-      <s:c r="E35" s="1"/>
+      <s:c r="D35" s="1" t="n">
+        <s:v>437.23</s:v>
+      </s:c>
+      <s:c r="E35" s="1" t="n">
+        <s:v>401.89</s:v>
+      </s:c>
       <s:c r="F35" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -5802,8 +5938,12 @@
       <s:c r="C36" s="1" t="n">
         <s:v>9</s:v>
       </s:c>
-      <s:c r="D36" s="1"/>
-      <s:c r="E36" s="1"/>
+      <s:c r="D36" s="1" t="n">
+        <s:v>437.23</s:v>
+      </s:c>
+      <s:c r="E36" s="1" t="n">
+        <s:v>381.45</s:v>
+      </s:c>
       <s:c r="F36" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -5848,8 +5988,12 @@
       <s:c r="C37" s="1" t="n">
         <s:v>9</s:v>
       </s:c>
-      <s:c r="D37" s="1"/>
-      <s:c r="E37" s="1"/>
+      <s:c r="D37" s="1" t="n">
+        <s:v>437.23</s:v>
+      </s:c>
+      <s:c r="E37" s="1" t="n">
+        <s:v>365.27</s:v>
+      </s:c>
       <s:c r="F37" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -5894,8 +6038,12 @@
       <s:c r="C38" s="1" t="n">
         <s:v>10</s:v>
       </s:c>
-      <s:c r="D38" s="1"/>
-      <s:c r="E38" s="1"/>
+      <s:c r="D38" s="1" t="n">
+        <s:v>349.42</s:v>
+      </s:c>
+      <s:c r="E38" s="1" t="n">
+        <s:v>353.42</s:v>
+      </s:c>
       <s:c r="F38" s="1" t="n">
         <s:v>-60</s:v>
       </s:c>
@@ -5940,8 +6088,12 @@
       <s:c r="C39" s="1" t="n">
         <s:v>10</s:v>
       </s:c>
-      <s:c r="D39" s="1"/>
-      <s:c r="E39" s="1"/>
+      <s:c r="D39" s="1" t="n">
+        <s:v>349.42</s:v>
+      </s:c>
+      <s:c r="E39" s="1" t="n">
+        <s:v>356.51</s:v>
+      </s:c>
       <s:c r="F39" s="1" t="n">
         <s:v>-270</s:v>
       </s:c>
@@ -5986,8 +6138,12 @@
       <s:c r="C40" s="1" t="n">
         <s:v>10</s:v>
       </s:c>
-      <s:c r="D40" s="1"/>
-      <s:c r="E40" s="1"/>
+      <s:c r="D40" s="1" t="n">
+        <s:v>349.42</s:v>
+      </s:c>
+      <s:c r="E40" s="1" t="n">
+        <s:v>353.42</s:v>
+      </s:c>
       <s:c r="F40" s="1" t="n">
         <s:v>-500</s:v>
       </s:c>
@@ -6032,8 +6188,12 @@
       <s:c r="C41" s="1" t="n">
         <s:v>10</s:v>
       </s:c>
-      <s:c r="D41" s="1"/>
-      <s:c r="E41" s="1"/>
+      <s:c r="D41" s="1" t="n">
+        <s:v>349.42</s:v>
+      </s:c>
+      <s:c r="E41" s="1" t="n">
+        <s:v>352.63</s:v>
+      </s:c>
       <s:c r="F41" s="1" t="n">
         <s:v>-730</s:v>
       </s:c>
@@ -6078,8 +6238,12 @@
       <s:c r="C42" s="1" t="n">
         <s:v>11</s:v>
       </s:c>
-      <s:c r="D42" s="1"/>
-      <s:c r="E42" s="1"/>
+      <s:c r="D42" s="1" t="n">
+        <s:v>349.42</s:v>
+      </s:c>
+      <s:c r="E42" s="1" t="n">
+        <s:v>363.86</s:v>
+      </s:c>
       <s:c r="F42" s="1" t="n">
         <s:v>-1352</s:v>
       </s:c>
@@ -6124,8 +6288,12 @@
       <s:c r="C43" s="1" t="n">
         <s:v>11</s:v>
       </s:c>
-      <s:c r="D43" s="1"/>
-      <s:c r="E43" s="1"/>
+      <s:c r="D43" s="1" t="n">
+        <s:v>349.42</s:v>
+      </s:c>
+      <s:c r="E43" s="1" t="n">
+        <s:v>353.35</s:v>
+      </s:c>
       <s:c r="F43" s="1" t="n">
         <s:v>-1527</s:v>
       </s:c>
@@ -6170,8 +6338,12 @@
       <s:c r="C44" s="1" t="n">
         <s:v>11</s:v>
       </s:c>
-      <s:c r="D44" s="1"/>
-      <s:c r="E44" s="1"/>
+      <s:c r="D44" s="1" t="n">
+        <s:v>349.42</s:v>
+      </s:c>
+      <s:c r="E44" s="1" t="n">
+        <s:v>353.42</s:v>
+      </s:c>
       <s:c r="F44" s="1" t="n">
         <s:v>-1673</s:v>
       </s:c>
@@ -6216,8 +6388,12 @@
       <s:c r="C45" s="1" t="n">
         <s:v>11</s:v>
       </s:c>
-      <s:c r="D45" s="1"/>
-      <s:c r="E45" s="1"/>
+      <s:c r="D45" s="1" t="n">
+        <s:v>349.42</s:v>
+      </s:c>
+      <s:c r="E45" s="1" t="n">
+        <s:v>353.42</s:v>
+      </s:c>
       <s:c r="F45" s="1" t="n">
         <s:v>-1703</s:v>
       </s:c>
@@ -6262,8 +6438,12 @@
       <s:c r="C46" s="1" t="n">
         <s:v>12</s:v>
       </s:c>
-      <s:c r="D46" s="1"/>
-      <s:c r="E46" s="1"/>
+      <s:c r="D46" s="1" t="n">
+        <s:v>349.42</s:v>
+      </s:c>
+      <s:c r="E46" s="1" t="n">
+        <s:v>355.39</s:v>
+      </s:c>
       <s:c r="F46" s="1" t="n">
         <s:v>-1428</s:v>
       </s:c>
@@ -6308,8 +6488,12 @@
       <s:c r="C47" s="1" t="n">
         <s:v>12</s:v>
       </s:c>
-      <s:c r="D47" s="1"/>
-      <s:c r="E47" s="1"/>
+      <s:c r="D47" s="1" t="n">
+        <s:v>349.42</s:v>
+      </s:c>
+      <s:c r="E47" s="1" t="n">
+        <s:v>353.42</s:v>
+      </s:c>
       <s:c r="F47" s="1" t="n">
         <s:v>-1468</s:v>
       </s:c>
@@ -6354,8 +6538,12 @@
       <s:c r="C48" s="1" t="n">
         <s:v>12</s:v>
       </s:c>
-      <s:c r="D48" s="1"/>
-      <s:c r="E48" s="1"/>
+      <s:c r="D48" s="1" t="n">
+        <s:v>349.42</s:v>
+      </s:c>
+      <s:c r="E48" s="1" t="n">
+        <s:v>352.52</s:v>
+      </s:c>
       <s:c r="F48" s="1" t="n">
         <s:v>-1315</s:v>
       </s:c>
@@ -6400,8 +6588,12 @@
       <s:c r="C49" s="1" t="n">
         <s:v>12</s:v>
       </s:c>
-      <s:c r="D49" s="1"/>
-      <s:c r="E49" s="1"/>
+      <s:c r="D49" s="1" t="n">
+        <s:v>349.42</s:v>
+      </s:c>
+      <s:c r="E49" s="1" t="n">
+        <s:v>350.67</s:v>
+      </s:c>
       <s:c r="F49" s="1" t="n">
         <s:v>-1220</s:v>
       </s:c>
@@ -6446,8 +6638,12 @@
       <s:c r="C50" s="1" t="n">
         <s:v>13</s:v>
       </s:c>
-      <s:c r="D50" s="1"/>
-      <s:c r="E50" s="1"/>
+      <s:c r="D50" s="1" t="n">
+        <s:v>349.42</s:v>
+      </s:c>
+      <s:c r="E50" s="1" t="n">
+        <s:v>380.29</s:v>
+      </s:c>
       <s:c r="F50" s="1" t="n">
         <s:v>-943</s:v>
       </s:c>
@@ -6492,8 +6688,12 @@
       <s:c r="C51" s="1" t="n">
         <s:v>13</s:v>
       </s:c>
-      <s:c r="D51" s="1"/>
-      <s:c r="E51" s="1"/>
+      <s:c r="D51" s="1" t="n">
+        <s:v>349.42</s:v>
+      </s:c>
+      <s:c r="E51" s="1" t="n">
+        <s:v>353.35</s:v>
+      </s:c>
       <s:c r="F51" s="1" t="n">
         <s:v>-943</s:v>
       </s:c>
@@ -6538,8 +6738,12 @@
       <s:c r="C52" s="1" t="n">
         <s:v>13</s:v>
       </s:c>
-      <s:c r="D52" s="1"/>
-      <s:c r="E52" s="1"/>
+      <s:c r="D52" s="1" t="n">
+        <s:v>349.42</s:v>
+      </s:c>
+      <s:c r="E52" s="1" t="n">
+        <s:v>353.42</s:v>
+      </s:c>
       <s:c r="F52" s="1" t="n">
         <s:v>-943</s:v>
       </s:c>
@@ -6584,8 +6788,12 @@
       <s:c r="C53" s="1" t="n">
         <s:v>13</s:v>
       </s:c>
-      <s:c r="D53" s="1"/>
-      <s:c r="E53" s="1"/>
+      <s:c r="D53" s="1" t="n">
+        <s:v>349.42</s:v>
+      </s:c>
+      <s:c r="E53" s="1" t="n">
+        <s:v>354.92</s:v>
+      </s:c>
       <s:c r="F53" s="1" t="n">
         <s:v>-923</s:v>
       </s:c>
@@ -6630,8 +6838,12 @@
       <s:c r="C54" s="1" t="n">
         <s:v>14</s:v>
       </s:c>
-      <s:c r="D54" s="1"/>
-      <s:c r="E54" s="1"/>
+      <s:c r="D54" s="1" t="n">
+        <s:v>349.42</s:v>
+      </s:c>
+      <s:c r="E54" s="1" t="n">
+        <s:v>363.7</s:v>
+      </s:c>
       <s:c r="F54" s="1" t="n">
         <s:v>-903</s:v>
       </s:c>
@@ -6676,8 +6888,12 @@
       <s:c r="C55" s="1" t="n">
         <s:v>14</s:v>
       </s:c>
-      <s:c r="D55" s="1"/>
-      <s:c r="E55" s="1"/>
+      <s:c r="D55" s="1" t="n">
+        <s:v>349.42</s:v>
+      </s:c>
+      <s:c r="E55" s="1" t="n">
+        <s:v>363.86</s:v>
+      </s:c>
       <s:c r="F55" s="1" t="n">
         <s:v>-843</s:v>
       </s:c>
@@ -6722,8 +6938,12 @@
       <s:c r="C56" s="1" t="n">
         <s:v>14</s:v>
       </s:c>
-      <s:c r="D56" s="1"/>
-      <s:c r="E56" s="1"/>
+      <s:c r="D56" s="1" t="n">
+        <s:v>349.42</s:v>
+      </s:c>
+      <s:c r="E56" s="1" t="n">
+        <s:v>355.39</s:v>
+      </s:c>
       <s:c r="F56" s="1" t="n">
         <s:v>-723</s:v>
       </s:c>
@@ -6768,8 +6988,12 @@
       <s:c r="C57" s="1" t="n">
         <s:v>14</s:v>
       </s:c>
-      <s:c r="D57" s="1"/>
-      <s:c r="E57" s="1"/>
+      <s:c r="D57" s="1" t="n">
+        <s:v>349.42</s:v>
+      </s:c>
+      <s:c r="E57" s="1" t="n">
+        <s:v>355</s:v>
+      </s:c>
       <s:c r="F57" s="1" t="n">
         <s:v>-713</s:v>
       </s:c>
@@ -6814,8 +7038,12 @@
       <s:c r="C58" s="1" t="n">
         <s:v>15</s:v>
       </s:c>
-      <s:c r="D58" s="1"/>
-      <s:c r="E58" s="1"/>
+      <s:c r="D58" s="1" t="n">
+        <s:v>349.42</s:v>
+      </s:c>
+      <s:c r="E58" s="1" t="n">
+        <s:v>350.19</s:v>
+      </s:c>
       <s:c r="F58" s="1" t="n">
         <s:v>-483</s:v>
       </s:c>
@@ -6860,8 +7088,12 @@
       <s:c r="C59" s="1" t="n">
         <s:v>15</s:v>
       </s:c>
-      <s:c r="D59" s="1"/>
-      <s:c r="E59" s="1"/>
+      <s:c r="D59" s="1" t="n">
+        <s:v>349.42</s:v>
+      </s:c>
+      <s:c r="E59" s="1" t="n">
+        <s:v>350.67</s:v>
+      </s:c>
       <s:c r="F59" s="1" t="n">
         <s:v>-323</s:v>
       </s:c>
@@ -6906,8 +7138,12 @@
       <s:c r="C60" s="1" t="n">
         <s:v>15</s:v>
       </s:c>
-      <s:c r="D60" s="1"/>
-      <s:c r="E60" s="1"/>
+      <s:c r="D60" s="1" t="n">
+        <s:v>349.42</s:v>
+      </s:c>
+      <s:c r="E60" s="1" t="n">
+        <s:v>364.6</s:v>
+      </s:c>
       <s:c r="F60" s="1" t="n">
         <s:v>-260</s:v>
       </s:c>
@@ -6952,8 +7188,12 @@
       <s:c r="C61" s="1" t="n">
         <s:v>15</s:v>
       </s:c>
-      <s:c r="D61" s="1"/>
-      <s:c r="E61" s="1"/>
+      <s:c r="D61" s="1" t="n">
+        <s:v>349.42</s:v>
+      </s:c>
+      <s:c r="E61" s="1" t="n">
+        <s:v>365.55</s:v>
+      </s:c>
       <s:c r="F61" s="1" t="n">
         <s:v>-90</s:v>
       </s:c>
@@ -6998,8 +7238,12 @@
       <s:c r="C62" s="1" t="n">
         <s:v>16</s:v>
       </s:c>
-      <s:c r="D62" s="1"/>
-      <s:c r="E62" s="1"/>
+      <s:c r="D62" s="1" t="n">
+        <s:v>427.51</s:v>
+      </s:c>
+      <s:c r="E62" s="1" t="n">
+        <s:v>365.66</s:v>
+      </s:c>
       <s:c r="F62" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -7044,8 +7288,12 @@
       <s:c r="C63" s="1" t="n">
         <s:v>16</s:v>
       </s:c>
-      <s:c r="D63" s="1"/>
-      <s:c r="E63" s="1"/>
+      <s:c r="D63" s="1" t="n">
+        <s:v>427.51</s:v>
+      </s:c>
+      <s:c r="E63" s="1" t="n">
+        <s:v>366.61</s:v>
+      </s:c>
       <s:c r="F63" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -7090,8 +7338,12 @@
       <s:c r="C64" s="1" t="n">
         <s:v>16</s:v>
       </s:c>
-      <s:c r="D64" s="1"/>
-      <s:c r="E64" s="1"/>
+      <s:c r="D64" s="1" t="n">
+        <s:v>427.51</s:v>
+      </s:c>
+      <s:c r="E64" s="1" t="n">
+        <s:v>393.36</s:v>
+      </s:c>
       <s:c r="F64" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -7136,8 +7388,12 @@
       <s:c r="C65" s="1" t="n">
         <s:v>16</s:v>
       </s:c>
-      <s:c r="D65" s="1"/>
-      <s:c r="E65" s="1"/>
+      <s:c r="D65" s="1" t="n">
+        <s:v>427.51</s:v>
+      </s:c>
+      <s:c r="E65" s="1" t="n">
+        <s:v>395.22</s:v>
+      </s:c>
       <s:c r="F65" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -7182,8 +7438,12 @@
       <s:c r="C66" s="1" t="n">
         <s:v>17</s:v>
       </s:c>
-      <s:c r="D66" s="1"/>
-      <s:c r="E66" s="1"/>
+      <s:c r="D66" s="1" t="n">
+        <s:v>464.55</s:v>
+      </s:c>
+      <s:c r="E66" s="1" t="n">
+        <s:v>389.67</s:v>
+      </s:c>
       <s:c r="F66" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -7228,8 +7488,12 @@
       <s:c r="C67" s="1" t="n">
         <s:v>17</s:v>
       </s:c>
-      <s:c r="D67" s="1"/>
-      <s:c r="E67" s="1"/>
+      <s:c r="D67" s="1" t="n">
+        <s:v>464.55</s:v>
+      </s:c>
+      <s:c r="E67" s="1" t="n">
+        <s:v>383.5</s:v>
+      </s:c>
       <s:c r="F67" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -7274,8 +7538,12 @@
       <s:c r="C68" s="1" t="n">
         <s:v>17</s:v>
       </s:c>
-      <s:c r="D68" s="1"/>
-      <s:c r="E68" s="1"/>
+      <s:c r="D68" s="1" t="n">
+        <s:v>464.55</s:v>
+      </s:c>
+      <s:c r="E68" s="1" t="n">
+        <s:v>382.6</s:v>
+      </s:c>
       <s:c r="F68" s="1" t="n">
         <s:v>100</s:v>
       </s:c>
@@ -7320,8 +7588,12 @@
       <s:c r="C69" s="1" t="n">
         <s:v>17</s:v>
       </s:c>
-      <s:c r="D69" s="1"/>
-      <s:c r="E69" s="1"/>
+      <s:c r="D69" s="1" t="n">
+        <s:v>464.55</s:v>
+      </s:c>
+      <s:c r="E69" s="1" t="n">
+        <s:v>393.36</s:v>
+      </s:c>
       <s:c r="F69" s="1" t="n">
         <s:v>260</s:v>
       </s:c>
@@ -7366,8 +7638,12 @@
       <s:c r="C70" s="1" t="n">
         <s:v>18</s:v>
       </s:c>
-      <s:c r="D70" s="1"/>
-      <s:c r="E70" s="1"/>
+      <s:c r="D70" s="1" t="n">
+        <s:v>398.01</s:v>
+      </s:c>
+      <s:c r="E70" s="1" t="n">
+        <s:v>373.83</s:v>
+      </s:c>
       <s:c r="F70" s="1" t="n">
         <s:v>530</s:v>
       </s:c>
@@ -7412,8 +7688,12 @@
       <s:c r="C71" s="1" t="n">
         <s:v>18</s:v>
       </s:c>
-      <s:c r="D71" s="1"/>
-      <s:c r="E71" s="1"/>
+      <s:c r="D71" s="1" t="n">
+        <s:v>398.01</s:v>
+      </s:c>
+      <s:c r="E71" s="1" t="n">
+        <s:v>402.98</s:v>
+      </s:c>
       <s:c r="F71" s="1" t="n">
         <s:v>713</s:v>
       </s:c>
@@ -7458,8 +7738,12 @@
       <s:c r="C72" s="1" t="n">
         <s:v>18</s:v>
       </s:c>
-      <s:c r="D72" s="1"/>
-      <s:c r="E72" s="1"/>
+      <s:c r="D72" s="1" t="n">
+        <s:v>398.01</s:v>
+      </s:c>
+      <s:c r="E72" s="1" t="n">
+        <s:v>368.35</s:v>
+      </s:c>
       <s:c r="F72" s="1" t="n">
         <s:v>873</s:v>
       </s:c>
@@ -7504,8 +7788,12 @@
       <s:c r="C73" s="1" t="n">
         <s:v>18</s:v>
       </s:c>
-      <s:c r="D73" s="1"/>
-      <s:c r="E73" s="1"/>
+      <s:c r="D73" s="1" t="n">
+        <s:v>398.01</s:v>
+      </s:c>
+      <s:c r="E73" s="1" t="n">
+        <s:v>389.92</s:v>
+      </s:c>
       <s:c r="F73" s="1" t="n">
         <s:v>923</s:v>
       </s:c>
@@ -7550,8 +7838,12 @@
       <s:c r="C74" s="1" t="n">
         <s:v>19</s:v>
       </s:c>
-      <s:c r="D74" s="1"/>
-      <s:c r="E74" s="1"/>
+      <s:c r="D74" s="1" t="n">
+        <s:v>413.64</s:v>
+      </s:c>
+      <s:c r="E74" s="1" t="n">
+        <s:v>381.45</s:v>
+      </s:c>
       <s:c r="F74" s="1" t="n">
         <s:v>873</s:v>
       </s:c>
@@ -7596,8 +7888,12 @@
       <s:c r="C75" s="1" t="n">
         <s:v>19</s:v>
       </s:c>
-      <s:c r="D75" s="1"/>
-      <s:c r="E75" s="1"/>
+      <s:c r="D75" s="1" t="n">
+        <s:v>413.64</s:v>
+      </s:c>
+      <s:c r="E75" s="1" t="n">
+        <s:v>400.39</s:v>
+      </s:c>
       <s:c r="F75" s="1" t="n">
         <s:v>933</s:v>
       </s:c>
@@ -7642,8 +7938,12 @@
       <s:c r="C76" s="1" t="n">
         <s:v>19</s:v>
       </s:c>
-      <s:c r="D76" s="1"/>
-      <s:c r="E76" s="1"/>
+      <s:c r="D76" s="1" t="n">
+        <s:v>413.64</s:v>
+      </s:c>
+      <s:c r="E76" s="1" t="n">
+        <s:v>400.8</s:v>
+      </s:c>
       <s:c r="F76" s="1" t="n">
         <s:v>913</s:v>
       </s:c>
@@ -7688,8 +7988,12 @@
       <s:c r="C77" s="1" t="n">
         <s:v>19</s:v>
       </s:c>
-      <s:c r="D77" s="1"/>
-      <s:c r="E77" s="1"/>
+      <s:c r="D77" s="1" t="n">
+        <s:v>413.64</s:v>
+      </s:c>
+      <s:c r="E77" s="1" t="n">
+        <s:v>400.86</s:v>
+      </s:c>
       <s:c r="F77" s="1" t="n">
         <s:v>853</s:v>
       </s:c>
@@ -7734,8 +8038,12 @@
       <s:c r="C78" s="1" t="n">
         <s:v>20</s:v>
       </s:c>
-      <s:c r="D78" s="1"/>
-      <s:c r="E78" s="1"/>
+      <s:c r="D78" s="1" t="n">
+        <s:v>413.64</s:v>
+      </s:c>
+      <s:c r="E78" s="1" t="n">
+        <s:v>400.3</s:v>
+      </s:c>
       <s:c r="F78" s="1" t="n">
         <s:v>873</s:v>
       </s:c>
@@ -7780,8 +8088,12 @@
       <s:c r="C79" s="1" t="n">
         <s:v>20</s:v>
       </s:c>
-      <s:c r="D79" s="1"/>
-      <s:c r="E79" s="1"/>
+      <s:c r="D79" s="1" t="n">
+        <s:v>413.64</s:v>
+      </s:c>
+      <s:c r="E79" s="1" t="n">
+        <s:v>399.66</s:v>
+      </s:c>
       <s:c r="F79" s="1" t="n">
         <s:v>663</s:v>
       </s:c>
@@ -7826,8 +8138,12 @@
       <s:c r="C80" s="1" t="n">
         <s:v>20</s:v>
       </s:c>
-      <s:c r="D80" s="1"/>
-      <s:c r="E80" s="1"/>
+      <s:c r="D80" s="1" t="n">
+        <s:v>413.64</s:v>
+      </s:c>
+      <s:c r="E80" s="1" t="n">
+        <s:v>401.7</s:v>
+      </s:c>
       <s:c r="F80" s="1" t="n">
         <s:v>470</s:v>
       </s:c>
@@ -7872,8 +8188,12 @@
       <s:c r="C81" s="1" t="n">
         <s:v>20</s:v>
       </s:c>
-      <s:c r="D81" s="1"/>
-      <s:c r="E81" s="1"/>
+      <s:c r="D81" s="1" t="n">
+        <s:v>413.64</s:v>
+      </s:c>
+      <s:c r="E81" s="1" t="n">
+        <s:v>403.23</s:v>
+      </s:c>
       <s:c r="F81" s="1" t="n">
         <s:v>290</s:v>
       </s:c>
@@ -7918,8 +8238,12 @@
       <s:c r="C82" s="1" t="n">
         <s:v>21</s:v>
       </s:c>
-      <s:c r="D82" s="1"/>
-      <s:c r="E82" s="1"/>
+      <s:c r="D82" s="1" t="n">
+        <s:v>413.64</s:v>
+      </s:c>
+      <s:c r="E82" s="1" t="n">
+        <s:v>420.64</s:v>
+      </s:c>
       <s:c r="F82" s="1" t="n">
         <s:v>160</s:v>
       </s:c>
@@ -7964,8 +8288,12 @@
       <s:c r="C83" s="1" t="n">
         <s:v>21</s:v>
       </s:c>
-      <s:c r="D83" s="1"/>
-      <s:c r="E83" s="1"/>
+      <s:c r="D83" s="1" t="n">
+        <s:v>413.64</s:v>
+      </s:c>
+      <s:c r="E83" s="1" t="n">
+        <s:v>402.98</s:v>
+      </s:c>
       <s:c r="F83" s="1" t="n">
         <s:v>130</s:v>
       </s:c>
@@ -8010,8 +8338,12 @@
       <s:c r="C84" s="1" t="n">
         <s:v>21</s:v>
       </s:c>
-      <s:c r="D84" s="1"/>
-      <s:c r="E84" s="1"/>
+      <s:c r="D84" s="1" t="n">
+        <s:v>413.64</s:v>
+      </s:c>
+      <s:c r="E84" s="1" t="n">
+        <s:v>401.39</s:v>
+      </s:c>
       <s:c r="F84" s="1" t="n">
         <s:v>90</s:v>
       </s:c>
@@ -8056,8 +8388,12 @@
       <s:c r="C85" s="1" t="n">
         <s:v>21</s:v>
       </s:c>
-      <s:c r="D85" s="1"/>
-      <s:c r="E85" s="1"/>
+      <s:c r="D85" s="1" t="n">
+        <s:v>413.64</s:v>
+      </s:c>
+      <s:c r="E85" s="1" t="n">
+        <s:v>401.7</s:v>
+      </s:c>
       <s:c r="F85" s="1" t="n">
         <s:v>90</s:v>
       </s:c>
@@ -8102,8 +8438,12 @@
       <s:c r="C86" s="1" t="n">
         <s:v>22</s:v>
       </s:c>
-      <s:c r="D86" s="1"/>
-      <s:c r="E86" s="1"/>
+      <s:c r="D86" s="1" t="n">
+        <s:v>413.64</s:v>
+      </s:c>
+      <s:c r="E86" s="1" t="n">
+        <s:v>399.91</s:v>
+      </s:c>
       <s:c r="F86" s="1" t="n">
         <s:v>130</s:v>
       </s:c>
@@ -8148,8 +8488,12 @@
       <s:c r="C87" s="1" t="n">
         <s:v>22</s:v>
       </s:c>
-      <s:c r="D87" s="1"/>
-      <s:c r="E87" s="1"/>
+      <s:c r="D87" s="1" t="n">
+        <s:v>413.64</s:v>
+      </s:c>
+      <s:c r="E87" s="1" t="n">
+        <s:v>409.02</s:v>
+      </s:c>
       <s:c r="F87" s="1" t="n">
         <s:v>160</s:v>
       </s:c>
@@ -8194,8 +8538,12 @@
       <s:c r="C88" s="1" t="n">
         <s:v>22</s:v>
       </s:c>
-      <s:c r="D88" s="1"/>
-      <s:c r="E88" s="1"/>
+      <s:c r="D88" s="1" t="n">
+        <s:v>413.64</s:v>
+      </s:c>
+      <s:c r="E88" s="1" t="n">
+        <s:v>403</s:v>
+      </s:c>
       <s:c r="F88" s="1" t="n">
         <s:v>230</s:v>
       </s:c>
@@ -8240,8 +8588,12 @@
       <s:c r="C89" s="1" t="n">
         <s:v>22</s:v>
       </s:c>
-      <s:c r="D89" s="1"/>
-      <s:c r="E89" s="1"/>
+      <s:c r="D89" s="1" t="n">
+        <s:v>413.64</s:v>
+      </s:c>
+      <s:c r="E89" s="1" t="n">
+        <s:v>433.23</s:v>
+      </s:c>
       <s:c r="F89" s="1" t="n">
         <s:v>420</s:v>
       </s:c>
@@ -8286,8 +8638,12 @@
       <s:c r="C90" s="1" t="n">
         <s:v>23</s:v>
       </s:c>
-      <s:c r="D90" s="1"/>
-      <s:c r="E90" s="1"/>
+      <s:c r="D90" s="1" t="n">
+        <s:v>413.64</s:v>
+      </s:c>
+      <s:c r="E90" s="1" t="n">
+        <s:v>431.69</s:v>
+      </s:c>
       <s:c r="F90" s="1" t="n">
         <s:v>939</s:v>
       </s:c>
@@ -8332,8 +8688,12 @@
       <s:c r="C91" s="1" t="n">
         <s:v>23</s:v>
       </s:c>
-      <s:c r="D91" s="1"/>
-      <s:c r="E91" s="1"/>
+      <s:c r="D91" s="1" t="n">
+        <s:v>422.27</s:v>
+      </s:c>
+      <s:c r="E91" s="1" t="n">
+        <s:v>431.32</s:v>
+      </s:c>
       <s:c r="F91" s="1" t="n">
         <s:v>1232</s:v>
       </s:c>
@@ -8378,8 +8738,12 @@
       <s:c r="C92" s="1" t="n">
         <s:v>23</s:v>
       </s:c>
-      <s:c r="D92" s="1"/>
-      <s:c r="E92" s="1"/>
+      <s:c r="D92" s="1" t="n">
+        <s:v>422.27</s:v>
+      </s:c>
+      <s:c r="E92" s="1" t="n">
+        <s:v>431.32</s:v>
+      </s:c>
       <s:c r="F92" s="1" t="n">
         <s:v>1558</s:v>
       </s:c>
@@ -8424,8 +8788,12 @@
       <s:c r="C93" s="1" t="n">
         <s:v>23</s:v>
       </s:c>
-      <s:c r="D93" s="1"/>
-      <s:c r="E93" s="1"/>
+      <s:c r="D93" s="1" t="n">
+        <s:v>422.27</s:v>
+      </s:c>
+      <s:c r="E93" s="1" t="n">
+        <s:v>433.23</s:v>
+      </s:c>
       <s:c r="F93" s="1" t="n">
         <s:v>1498</s:v>
       </s:c>
@@ -8470,8 +8838,12 @@
       <s:c r="C94" s="1" t="n">
         <s:v>24</s:v>
       </s:c>
-      <s:c r="D94" s="1"/>
-      <s:c r="E94" s="1"/>
+      <s:c r="D94" s="1" t="n">
+        <s:v>413.64</s:v>
+      </s:c>
+      <s:c r="E94" s="1" t="n">
+        <s:v>432.45</s:v>
+      </s:c>
       <s:c r="F94" s="1" t="n">
         <s:v>1423</s:v>
       </s:c>
@@ -8516,8 +8888,12 @@
       <s:c r="C95" s="1" t="n">
         <s:v>24</s:v>
       </s:c>
-      <s:c r="D95" s="1"/>
-      <s:c r="E95" s="1"/>
+      <s:c r="D95" s="1" t="n">
+        <s:v>413.64</s:v>
+      </s:c>
+      <s:c r="E95" s="1" t="n">
+        <s:v>428.25</s:v>
+      </s:c>
       <s:c r="F95" s="1" t="n">
         <s:v>1453</s:v>
       </s:c>
@@ -8562,8 +8938,12 @@
       <s:c r="C96" s="1" t="n">
         <s:v>24</s:v>
       </s:c>
-      <s:c r="D96" s="1"/>
-      <s:c r="E96" s="1"/>
+      <s:c r="D96" s="1" t="n">
+        <s:v>413.64</s:v>
+      </s:c>
+      <s:c r="E96" s="1" t="n">
+        <s:v>403.92</s:v>
+      </s:c>
       <s:c r="F96" s="1" t="n">
         <s:v>987</s:v>
       </s:c>
@@ -8610,8 +8990,12 @@
       <s:c r="C97" s="1" t="n">
         <s:v>24</s:v>
       </s:c>
-      <s:c r="D97" s="1"/>
-      <s:c r="E97" s="1"/>
+      <s:c r="D97" s="1" t="n">
+        <s:v>413.64</s:v>
+      </s:c>
+      <s:c r="E97" s="1" t="n">
+        <s:v>407.69</s:v>
+      </s:c>
       <s:c r="F97" s="1" t="n">
         <s:v>714</s:v>
       </s:c>
